--- a/outputs/daily/hr_rankings_2026-10-19.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-19.xlsx
@@ -975,24 +975,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>666176</t>
+          <t>666018</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jo Adell</t>
+          <t>Jonathan Aranda</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -1005,14 +1005,14 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>51.4</v>
+        <v>50.4</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>53.3</v>
+        <v>48.9</v>
       </c>
       <c r="Q3" t="n">
         <v>41.2</v>
@@ -1039,13 +1039,13 @@
         <v>27.6</v>
       </c>
       <c r="S3" t="n">
-        <v>90.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T3" t="n">
         <v>60</v>
       </c>
       <c r="U3" t="n">
-        <v>34.9</v>
+        <v>28.9</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -1101,12 +1101,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 1 HR</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1131,67 +1131,67 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>46.43</t>
+          <t>48.55</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>90.79</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>103.0119</t>
+          <t>101.2282</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.4755</t>
+          <t>0.4611</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.2176</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.3398</t>
+          <t>0.3547</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>77.46</t>
+          <t>70.36</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>72.67</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>33.13</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>27.56</t>
+          <t>30.13</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.1874</t>
+          <t>0.1639</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr"/>
@@ -1215,24 +1215,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>666018</t>
+          <t>666176</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jonathan Aranda</t>
+          <t>Jo Adell</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -1245,14 +1245,26 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Freddy Peralta</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>642547</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L4" t="n">
-        <v>50.4</v>
+        <v>48.7</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1270,22 +1282,22 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>48.9</v>
+        <v>53.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>41.2</v>
+        <v>33.4</v>
       </c>
       <c r="R4" t="n">
         <v>27.6</v>
       </c>
       <c r="S4" t="n">
-        <v>95.5</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U4" t="n">
-        <v>28.9</v>
+        <v>34.9</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -1299,7 +1311,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1324,7 +1336,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
@@ -1341,12 +1353,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1356,12 +1368,12 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Last 7 games: 6/26, 1 HR</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -1371,75 +1383,99 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>46.43</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>90.79</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>101.2282</t>
+          <t>103.0119</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4611</t>
+          <t>0.4755</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>0.2176</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3547</t>
+          <t>0.3398</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>70.36</t>
+          <t>77.46</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>72.67</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>33.13</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>27.56</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>27.2</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.1639</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
+          <t>0.1874</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>6.85</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>36.39</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>87.72</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>0.368</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0.1417</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>28.41</t>
+        </is>
+      </c>
       <c r="BG4" t="inlineStr"/>
       <c r="BH4" t="inlineStr"/>
       <c r="BI4" t="inlineStr">
@@ -1488,11 +1524,23 @@
           <t>3</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Freddy Peralta</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>642547</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L5" t="n">
-        <v>46.7</v>
+        <v>46.6</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1506,14 +1554,14 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
         <v>35.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>41.2</v>
+        <v>33.4</v>
       </c>
       <c r="R5" t="n">
         <v>27.6</v>
@@ -1522,7 +1570,7 @@
         <v>92.09999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U5" t="n">
         <v>56.2</v>
@@ -1564,7 +1612,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>H:2026 P:</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -1601,7 +1649,7 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1674,12 +1722,36 @@
           <t>0.17</t>
         </is>
       </c>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>6.85</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>36.39</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>87.72</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>0.368</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0.1417</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>28.41</t>
+        </is>
+      </c>
       <c r="BG5" t="inlineStr"/>
       <c r="BH5" t="inlineStr"/>
       <c r="BI5" t="inlineStr">
@@ -2175,12 +2247,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>608070</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2205,14 +2277,26 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Freddy Peralta</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>642547</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L8" t="n">
-        <v>43.6</v>
+        <v>43.3</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2226,26 +2310,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>25.8</v>
+        <v>36.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>40.2</v>
+        <v>33.4</v>
       </c>
       <c r="R8" t="n">
         <v>27.6</v>
       </c>
       <c r="S8" t="n">
-        <v>95.5</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U8" t="n">
-        <v>23.4</v>
+        <v>10.1</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -2259,7 +2343,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -2284,7 +2368,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr"/>
@@ -2301,12 +2385,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -2316,12 +2400,12 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/29, 0 HR</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -2331,75 +2415,99 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>88.69</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>99.2749</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4075</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1361</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3301</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>12.84</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>50.41</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1591</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr"/>
-      <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="inlineStr"/>
-      <c r="BF8" t="inlineStr"/>
+          <t>0.1803</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>6.85</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>36.39</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>87.72</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>0.368</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0.1417</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>28.41</t>
+        </is>
+      </c>
       <c r="BG8" t="inlineStr"/>
       <c r="BH8" t="inlineStr"/>
       <c r="BI8" t="inlineStr">
@@ -2415,12 +2523,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>608070</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Jose Ramirez</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2445,14 +2553,26 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Freddy Peralta</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>642547</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L9" t="n">
-        <v>43.4</v>
+        <v>41.5</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2466,26 +2586,26 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>36.3</v>
+        <v>25.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>41.2</v>
+        <v>31.6</v>
       </c>
       <c r="R9" t="n">
         <v>27.6</v>
       </c>
       <c r="S9" t="n">
-        <v>81.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T9" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="U9" t="n">
-        <v>10.1</v>
+        <v>23.4</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -2499,7 +2619,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -2524,7 +2644,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr"/>
@@ -2541,12 +2661,12 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -2556,12 +2676,12 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Last 7 games: 8/29, 0 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -2571,75 +2691,99 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>88.69</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>99.2749</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.4075</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1361</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3301</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>12.84</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>50.41</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1803</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr"/>
-      <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="inlineStr"/>
+          <t>0.1591</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>6.85</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>36.39</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>87.72</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>0.368</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>0.1417</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>28.41</t>
+        </is>
+      </c>
       <c r="BG9" t="inlineStr"/>
       <c r="BH9" t="inlineStr"/>
       <c r="BI9" t="inlineStr">
@@ -2688,11 +2832,23 @@
           <t>7</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Freddy Peralta</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>642547</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L10" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -2713,7 +2869,7 @@
         <v>32.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>40.2</v>
+        <v>31.6</v>
       </c>
       <c r="R10" t="n">
         <v>27.6</v>
@@ -2764,7 +2920,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr"/>
@@ -2801,7 +2957,7 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -2874,12 +3030,36 @@
           <t>0.1212</t>
         </is>
       </c>
-      <c r="BA10" t="inlineStr"/>
-      <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="inlineStr"/>
-      <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="inlineStr"/>
-      <c r="BF10" t="inlineStr"/>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>6.85</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>36.39</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>87.72</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>0.368</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>0.1417</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>28.41</t>
+        </is>
+      </c>
       <c r="BG10" t="inlineStr"/>
       <c r="BH10" t="inlineStr"/>
       <c r="BI10" t="inlineStr">
@@ -2928,11 +3108,23 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Freddy Peralta</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>642547</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L11" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -2946,14 +3138,14 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
         <v>20.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>41.2</v>
+        <v>33.4</v>
       </c>
       <c r="R11" t="n">
         <v>27.6</v>
@@ -2962,7 +3154,7 @@
         <v>71.7</v>
       </c>
       <c r="T11" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U11" t="n">
         <v>12</v>
@@ -3004,7 +3196,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>H:2026 P:</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -3041,7 +3233,7 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -3114,12 +3306,36 @@
           <t>0.163</t>
         </is>
       </c>
-      <c r="BA11" t="inlineStr"/>
-      <c r="BB11" t="inlineStr"/>
-      <c r="BC11" t="inlineStr"/>
-      <c r="BD11" t="inlineStr"/>
-      <c r="BE11" t="inlineStr"/>
-      <c r="BF11" t="inlineStr"/>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>6.85</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>36.39</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>87.72</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>0.368</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>0.1417</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>28.41</t>
+        </is>
+      </c>
       <c r="BG11" t="inlineStr"/>
       <c r="BH11" t="inlineStr"/>
       <c r="BI11" t="inlineStr">
@@ -3408,11 +3624,23 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Freddy Peralta</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>642547</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L13" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3426,14 +3654,14 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
         <v>2.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>41.2</v>
+        <v>33.4</v>
       </c>
       <c r="R13" t="n">
         <v>27.6</v>
@@ -3442,7 +3670,7 @@
         <v>88.7</v>
       </c>
       <c r="T13" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
         <v>43.1</v>
@@ -3484,7 +3712,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr"/>
@@ -3521,7 +3749,7 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -3594,12 +3822,36 @@
           <t>0.0775</t>
         </is>
       </c>
-      <c r="BA13" t="inlineStr"/>
-      <c r="BB13" t="inlineStr"/>
-      <c r="BC13" t="inlineStr"/>
-      <c r="BD13" t="inlineStr"/>
-      <c r="BE13" t="inlineStr"/>
-      <c r="BF13" t="inlineStr"/>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>6.85</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>36.39</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>87.72</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>0.368</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>0.1417</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>28.41</t>
+        </is>
+      </c>
       <c r="BG13" t="inlineStr"/>
       <c r="BH13" t="inlineStr"/>
       <c r="BI13" t="inlineStr">
@@ -3648,11 +3900,23 @@
           <t>9</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Freddy Peralta</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>642547</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L14" t="n">
-        <v>34.3</v>
+        <v>32.3</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -3673,7 +3937,7 @@
         <v>13.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>40.2</v>
+        <v>31.6</v>
       </c>
       <c r="R14" t="n">
         <v>27.6</v>
@@ -3724,7 +3988,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -3761,7 +4025,7 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -3834,12 +4098,36 @@
           <t>0.1287</t>
         </is>
       </c>
-      <c r="BA14" t="inlineStr"/>
-      <c r="BB14" t="inlineStr"/>
-      <c r="BC14" t="inlineStr"/>
-      <c r="BD14" t="inlineStr"/>
-      <c r="BE14" t="inlineStr"/>
-      <c r="BF14" t="inlineStr"/>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>6.85</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>36.39</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>87.72</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>0.368</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>0.1417</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>28.41</t>
+        </is>
+      </c>
       <c r="BG14" t="inlineStr"/>
       <c r="BH14" t="inlineStr"/>
       <c r="BI14" t="inlineStr">
@@ -4368,11 +4656,23 @@
           <t>8</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Freddy Peralta</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>642547</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L17" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4386,14 +4686,14 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
         <v>7.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>41.2</v>
+        <v>33.4</v>
       </c>
       <c r="R17" t="n">
         <v>27.6</v>
@@ -4402,7 +4702,7 @@
         <v>47.9</v>
       </c>
       <c r="T17" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U17" t="n">
         <v>38.3</v>
@@ -4444,7 +4744,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -4481,7 +4781,7 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -4554,12 +4854,36 @@
           <t>0.0707</t>
         </is>
       </c>
-      <c r="BA17" t="inlineStr"/>
-      <c r="BB17" t="inlineStr"/>
-      <c r="BC17" t="inlineStr"/>
-      <c r="BD17" t="inlineStr"/>
-      <c r="BE17" t="inlineStr"/>
-      <c r="BF17" t="inlineStr"/>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>6.85</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>36.39</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>87.72</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>0.368</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>0.1417</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>28.41</t>
+        </is>
+      </c>
       <c r="BG17" t="inlineStr"/>
       <c r="BH17" t="inlineStr"/>
       <c r="BI17" t="inlineStr">
@@ -5621,24 +5945,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>666176</t>
+          <t>666018</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jo Adell</t>
+          <t>Jonathan Aranda</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -5651,14 +5975,14 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>51.4</v>
+        <v>50.4</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -5676,7 +6000,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>53.3</v>
+        <v>48.9</v>
       </c>
       <c r="Q3" t="n">
         <v>41.2</v>
@@ -5685,13 +6009,13 @@
         <v>27.6</v>
       </c>
       <c r="S3" t="n">
-        <v>90.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T3" t="n">
         <v>60</v>
       </c>
       <c r="U3" t="n">
-        <v>34.9</v>
+        <v>28.9</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -5705,7 +6029,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -5747,12 +6071,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -5762,7 +6086,7 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 1 HR</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -5777,67 +6101,67 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>46.43</t>
+          <t>48.55</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>90.79</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>103.0119</t>
+          <t>101.2282</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.4755</t>
+          <t>0.4611</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.2176</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.3398</t>
+          <t>0.3547</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>77.46</t>
+          <t>70.36</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>72.67</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>33.13</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>27.56</t>
+          <t>30.13</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.1874</t>
+          <t>0.1639</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr"/>
@@ -5861,24 +6185,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>666018</t>
+          <t>666176</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jonathan Aranda</t>
+          <t>Jo Adell</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -5891,14 +6215,26 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Freddy Peralta</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>642547</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L4" t="n">
-        <v>50.4</v>
+        <v>48.7</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -5916,22 +6252,22 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>48.9</v>
+        <v>53.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>41.2</v>
+        <v>33.4</v>
       </c>
       <c r="R4" t="n">
         <v>27.6</v>
       </c>
       <c r="S4" t="n">
-        <v>95.5</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U4" t="n">
-        <v>28.9</v>
+        <v>34.9</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -5945,7 +6281,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -5970,7 +6306,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
@@ -5987,12 +6323,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -6002,12 +6338,12 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Last 7 games: 6/26, 1 HR</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -6017,75 +6353,99 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>46.43</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>90.79</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>101.2282</t>
+          <t>103.0119</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4611</t>
+          <t>0.4755</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>0.2176</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3547</t>
+          <t>0.3398</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>70.36</t>
+          <t>77.46</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>72.67</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>33.13</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>27.56</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>27.2</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.1639</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
+          <t>0.1874</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>6.85</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>36.39</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>87.72</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>0.368</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0.1417</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>28.41</t>
+        </is>
+      </c>
       <c r="BG4" t="inlineStr"/>
       <c r="BH4" t="inlineStr"/>
       <c r="BI4" t="inlineStr">
@@ -6134,11 +6494,23 @@
           <t>3</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Freddy Peralta</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>642547</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L5" t="n">
-        <v>46.7</v>
+        <v>46.6</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -6152,14 +6524,14 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
         <v>35.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>41.2</v>
+        <v>33.4</v>
       </c>
       <c r="R5" t="n">
         <v>27.6</v>
@@ -6168,7 +6540,7 @@
         <v>92.09999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U5" t="n">
         <v>56.2</v>
@@ -6210,7 +6582,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>H:2026 P:</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -6247,7 +6619,7 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -6320,12 +6692,36 @@
           <t>0.17</t>
         </is>
       </c>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>6.85</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>36.39</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>87.72</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>0.368</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0.1417</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>28.41</t>
+        </is>
+      </c>
       <c r="BG5" t="inlineStr"/>
       <c r="BH5" t="inlineStr"/>
       <c r="BI5" t="inlineStr">
@@ -6821,12 +7217,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>608070</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -6851,14 +7247,26 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Freddy Peralta</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>642547</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L8" t="n">
-        <v>43.6</v>
+        <v>43.3</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -6872,26 +7280,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>25.8</v>
+        <v>36.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>40.2</v>
+        <v>33.4</v>
       </c>
       <c r="R8" t="n">
         <v>27.6</v>
       </c>
       <c r="S8" t="n">
-        <v>95.5</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U8" t="n">
-        <v>23.4</v>
+        <v>10.1</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -6905,7 +7313,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -6930,7 +7338,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr"/>
@@ -6947,12 +7355,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -6962,12 +7370,12 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/29, 0 HR</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -6977,75 +7385,99 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>88.69</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>99.2749</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4075</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1361</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3301</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>12.84</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>50.41</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1591</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr"/>
-      <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="inlineStr"/>
-      <c r="BF8" t="inlineStr"/>
+          <t>0.1803</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>6.85</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>36.39</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>87.72</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>0.368</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0.1417</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>28.41</t>
+        </is>
+      </c>
       <c r="BG8" t="inlineStr"/>
       <c r="BH8" t="inlineStr"/>
       <c r="BI8" t="inlineStr">
@@ -7061,12 +7493,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>608070</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Jose Ramirez</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -7091,14 +7523,26 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Freddy Peralta</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>642547</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L9" t="n">
-        <v>43.4</v>
+        <v>41.5</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -7112,26 +7556,26 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>36.3</v>
+        <v>25.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>41.2</v>
+        <v>31.6</v>
       </c>
       <c r="R9" t="n">
         <v>27.6</v>
       </c>
       <c r="S9" t="n">
-        <v>81.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T9" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="U9" t="n">
-        <v>10.1</v>
+        <v>23.4</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -7145,7 +7589,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -7170,7 +7614,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr"/>
@@ -7187,12 +7631,12 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -7202,12 +7646,12 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Last 7 games: 8/29, 0 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -7217,75 +7661,99 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>88.69</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>99.2749</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.4075</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1361</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3301</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>12.84</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>50.41</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1803</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr"/>
-      <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="inlineStr"/>
+          <t>0.1591</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>6.85</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>36.39</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>87.72</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>0.368</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>0.1417</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>28.41</t>
+        </is>
+      </c>
       <c r="BG9" t="inlineStr"/>
       <c r="BH9" t="inlineStr"/>
       <c r="BI9" t="inlineStr">
@@ -7334,11 +7802,23 @@
           <t>7</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Freddy Peralta</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>642547</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L10" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -7359,7 +7839,7 @@
         <v>32.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>40.2</v>
+        <v>31.6</v>
       </c>
       <c r="R10" t="n">
         <v>27.6</v>
@@ -7410,7 +7890,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr"/>
@@ -7447,7 +7927,7 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -7520,12 +8000,36 @@
           <t>0.1212</t>
         </is>
       </c>
-      <c r="BA10" t="inlineStr"/>
-      <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="inlineStr"/>
-      <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="inlineStr"/>
-      <c r="BF10" t="inlineStr"/>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>6.85</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>36.39</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>87.72</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>0.368</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>0.1417</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>28.41</t>
+        </is>
+      </c>
       <c r="BG10" t="inlineStr"/>
       <c r="BH10" t="inlineStr"/>
       <c r="BI10" t="inlineStr">
@@ -7574,11 +8078,23 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Freddy Peralta</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>642547</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L11" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -7592,14 +8108,14 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
         <v>20.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>41.2</v>
+        <v>33.4</v>
       </c>
       <c r="R11" t="n">
         <v>27.6</v>
@@ -7608,7 +8124,7 @@
         <v>71.7</v>
       </c>
       <c r="T11" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U11" t="n">
         <v>12</v>
@@ -7650,7 +8166,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>H:2026 P:</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -7687,7 +8203,7 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -7760,12 +8276,36 @@
           <t>0.163</t>
         </is>
       </c>
-      <c r="BA11" t="inlineStr"/>
-      <c r="BB11" t="inlineStr"/>
-      <c r="BC11" t="inlineStr"/>
-      <c r="BD11" t="inlineStr"/>
-      <c r="BE11" t="inlineStr"/>
-      <c r="BF11" t="inlineStr"/>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>6.85</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>36.39</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>87.72</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>0.368</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>0.1417</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>28.41</t>
+        </is>
+      </c>
       <c r="BG11" t="inlineStr"/>
       <c r="BH11" t="inlineStr"/>
       <c r="BI11" t="inlineStr">
@@ -8054,11 +8594,23 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Freddy Peralta</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>642547</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L13" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -8072,14 +8624,14 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
         <v>2.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>41.2</v>
+        <v>33.4</v>
       </c>
       <c r="R13" t="n">
         <v>27.6</v>
@@ -8088,7 +8640,7 @@
         <v>88.7</v>
       </c>
       <c r="T13" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
         <v>43.1</v>
@@ -8130,7 +8682,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr"/>
@@ -8167,7 +8719,7 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -8240,12 +8792,36 @@
           <t>0.0775</t>
         </is>
       </c>
-      <c r="BA13" t="inlineStr"/>
-      <c r="BB13" t="inlineStr"/>
-      <c r="BC13" t="inlineStr"/>
-      <c r="BD13" t="inlineStr"/>
-      <c r="BE13" t="inlineStr"/>
-      <c r="BF13" t="inlineStr"/>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>6.85</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>36.39</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>87.72</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>0.368</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>0.1417</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>28.41</t>
+        </is>
+      </c>
       <c r="BG13" t="inlineStr"/>
       <c r="BH13" t="inlineStr"/>
       <c r="BI13" t="inlineStr">
@@ -8294,11 +8870,23 @@
           <t>9</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Freddy Peralta</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>642547</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L14" t="n">
-        <v>34.3</v>
+        <v>32.3</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -8319,7 +8907,7 @@
         <v>13.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>40.2</v>
+        <v>31.6</v>
       </c>
       <c r="R14" t="n">
         <v>27.6</v>
@@ -8370,7 +8958,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -8407,7 +8995,7 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -8480,12 +9068,36 @@
           <t>0.1287</t>
         </is>
       </c>
-      <c r="BA14" t="inlineStr"/>
-      <c r="BB14" t="inlineStr"/>
-      <c r="BC14" t="inlineStr"/>
-      <c r="BD14" t="inlineStr"/>
-      <c r="BE14" t="inlineStr"/>
-      <c r="BF14" t="inlineStr"/>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>6.85</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>36.39</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>87.72</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>0.368</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>0.1417</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>28.41</t>
+        </is>
+      </c>
       <c r="BG14" t="inlineStr"/>
       <c r="BH14" t="inlineStr"/>
       <c r="BI14" t="inlineStr">
@@ -9014,11 +9626,23 @@
           <t>8</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Freddy Peralta</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>642547</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L17" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -9032,14 +9656,14 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
         <v>7.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>41.2</v>
+        <v>33.4</v>
       </c>
       <c r="R17" t="n">
         <v>27.6</v>
@@ -9048,7 +9672,7 @@
         <v>47.9</v>
       </c>
       <c r="T17" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U17" t="n">
         <v>38.3</v>
@@ -9090,7 +9714,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -9127,7 +9751,7 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -9200,12 +9824,36 @@
           <t>0.0707</t>
         </is>
       </c>
-      <c r="BA17" t="inlineStr"/>
-      <c r="BB17" t="inlineStr"/>
-      <c r="BC17" t="inlineStr"/>
-      <c r="BD17" t="inlineStr"/>
-      <c r="BE17" t="inlineStr"/>
-      <c r="BF17" t="inlineStr"/>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>6.85</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>36.39</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>87.72</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>0.368</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>0.1417</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>28.41</t>
+        </is>
+      </c>
       <c r="BG17" t="inlineStr"/>
       <c r="BH17" t="inlineStr"/>
       <c r="BI17" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-10-19.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-19.xlsx
@@ -765,14 +765,14 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>54.4</v>
+        <v>54.7</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>27.6</v>
       </c>
       <c r="S2" t="n">
-        <v>90.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T2" t="n">
         <v>60</v>
@@ -814,12 +814,12 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>72.67</t>
+          <t>72.74</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Yandy Diaz</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1797,14 +1797,14 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>46.6</v>
+        <v>46.4</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>43.3</v>
+        <v>41</v>
       </c>
       <c r="Q6" t="n">
         <v>41.2</v>
@@ -1831,13 +1831,13 @@
         <v>27.6</v>
       </c>
       <c r="S6" t="n">
-        <v>92.09999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="T6" t="n">
         <v>60</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>20.9</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1846,12 +1846,12 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1893,12 +1893,12 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1923,67 +1923,67 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>102.6273</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1288</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr"/>
@@ -2007,12 +2007,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>668723</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Ryan Vilade</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -2062,7 +2062,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>41</v>
+        <v>43.3</v>
       </c>
       <c r="Q7" t="n">
         <v>41.2</v>
@@ -2071,13 +2071,13 @@
         <v>27.6</v>
       </c>
       <c r="S7" t="n">
-        <v>88.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T7" t="n">
         <v>60</v>
       </c>
       <c r="U7" t="n">
-        <v>20.9</v>
+        <v>0</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -2086,12 +2086,12 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2163,67 +2163,67 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>50.43</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>91.42</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>102.6273</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.3949</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1562</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3174</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>75.84</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>37.37</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1617</t>
+          <t>0.1288</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr"/>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -2866,7 +2866,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
       <c r="Q10" t="n">
         <v>31.6</v>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>72.34</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -3075,24 +3075,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -3105,26 +3105,14 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Freddy Peralta</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>642547</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>36.9</v>
+        <v>37.9</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3138,26 +3126,26 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>20.9</v>
+        <v>10.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>33.4</v>
+        <v>41.2</v>
       </c>
       <c r="R11" t="n">
         <v>27.6</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U11" t="n">
-        <v>12</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -3166,24 +3154,24 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -3196,7 +3184,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -3213,27 +3201,27 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -3243,99 +3231,75 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>98.2866</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.163</t>
-        </is>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>6.85</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>36.39</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>87.72</t>
-        </is>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>0.368</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>0.1417</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>28.41</t>
-        </is>
-      </c>
+          <t>0.151</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr"/>
       <c r="BG11" t="inlineStr"/>
       <c r="BH11" t="inlineStr"/>
       <c r="BI11" t="inlineStr">
@@ -3351,24 +3315,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -3384,11 +3348,23 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Freddy Peralta</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>642547</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L12" t="n">
-        <v>36.5</v>
+        <v>36.9</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3402,14 +3378,14 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>10.6</v>
+        <v>21</v>
       </c>
       <c r="Q12" t="n">
-        <v>41.2</v>
+        <v>33.4</v>
       </c>
       <c r="R12" t="n">
         <v>27.6</v>
@@ -3418,10 +3394,10 @@
         <v>71.7</v>
       </c>
       <c r="T12" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>70.59999999999999</v>
+        <v>12</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -3430,24 +3406,24 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -3460,7 +3436,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -3477,27 +3453,27 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -3507,75 +3483,99 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>98.2866</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.123</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>72.68</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.151</t>
-        </is>
-      </c>
-      <c r="BA12" t="inlineStr"/>
-      <c r="BB12" t="inlineStr"/>
-      <c r="BC12" t="inlineStr"/>
-      <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="inlineStr"/>
-      <c r="BF12" t="inlineStr"/>
+          <t>0.163</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>6.85</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>36.39</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>87.72</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>0.368</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>0.1417</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>28.41</t>
+        </is>
+      </c>
       <c r="BG12" t="inlineStr"/>
       <c r="BH12" t="inlineStr"/>
       <c r="BI12" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -3867,24 +3867,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>677587</t>
+          <t>622761</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Jorge Mateo</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -3897,26 +3897,14 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Freddy Peralta</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>642547</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>32.3</v>
+        <v>33.9</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -3930,26 +3918,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>13.7</v>
+        <v>23.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>31.6</v>
+        <v>41.2</v>
       </c>
       <c r="R14" t="n">
         <v>27.6</v>
       </c>
       <c r="S14" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T14" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="U14" t="n">
-        <v>72.7</v>
+        <v>0.8</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -3958,24 +3946,24 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -3988,7 +3976,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -4005,27 +3993,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 2/16, 0 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -4035,99 +4023,75 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>6.76</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>35.51</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>97.253</t>
+          <t>98.4476</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3524</t>
+          <t>0.3271</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1067</t>
+          <t>0.1223</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.2943</t>
+          <t>0.2522</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>69.79</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>31.46</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>29.09</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.1287</t>
-        </is>
-      </c>
-      <c r="BA14" t="inlineStr">
-        <is>
-          <t>6.85</t>
-        </is>
-      </c>
-      <c r="BB14" t="inlineStr">
-        <is>
-          <t>36.39</t>
-        </is>
-      </c>
-      <c r="BC14" t="inlineStr">
-        <is>
-          <t>87.72</t>
-        </is>
-      </c>
-      <c r="BD14" t="inlineStr">
-        <is>
-          <t>0.368</t>
-        </is>
-      </c>
-      <c r="BE14" t="inlineStr">
-        <is>
-          <t>0.1417</t>
-        </is>
-      </c>
-      <c r="BF14" t="inlineStr">
-        <is>
-          <t>28.41</t>
-        </is>
-      </c>
+          <t>0.1044</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr"/>
+      <c r="BB14" t="inlineStr"/>
+      <c r="BC14" t="inlineStr"/>
+      <c r="BD14" t="inlineStr"/>
+      <c r="BE14" t="inlineStr"/>
+      <c r="BF14" t="inlineStr"/>
       <c r="BG14" t="inlineStr"/>
       <c r="BH14" t="inlineStr"/>
       <c r="BI14" t="inlineStr">
@@ -4143,12 +4107,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>663743</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Nick Fortes</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4173,14 +4137,14 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>31.8</v>
+        <v>32.9</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4198,7 +4162,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0.2</v>
+        <v>12.8</v>
       </c>
       <c r="Q15" t="n">
         <v>41.2</v>
@@ -4207,13 +4171,13 @@
         <v>27.6</v>
       </c>
       <c r="S15" t="n">
-        <v>81.90000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="T15" t="n">
         <v>60</v>
       </c>
       <c r="U15" t="n">
-        <v>15.3</v>
+        <v>18.3</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -4222,12 +4186,12 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -4269,22 +4233,22 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 2/17, 1 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -4299,67 +4263,67 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>36.15</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>86.03</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>99.0812</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3248</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.093</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.2721</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>72.49</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>50.84</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>18.36</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.1186</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr"/>
@@ -4383,24 +4347,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>689414</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -4413,14 +4377,26 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Freddy Peralta</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>642547</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L16" t="n">
-        <v>31.4</v>
+        <v>32.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4434,26 +4410,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>7.8</v>
+        <v>13.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>41.2</v>
+        <v>31.6</v>
       </c>
       <c r="R16" t="n">
         <v>27.6</v>
       </c>
       <c r="S16" t="n">
-        <v>59.8</v>
+        <v>40.2</v>
       </c>
       <c r="T16" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="U16" t="n">
-        <v>19.5</v>
+        <v>72.7</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -4462,24 +4438,24 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -4492,7 +4468,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -4509,27 +4485,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -4539,75 +4515,99 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>96.0847</t>
+          <t>97.253</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3556</t>
+          <t>0.3524</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.0997</t>
+          <t>0.1067</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3178</t>
+          <t>0.2943</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>68.03</t>
+          <t>69.79</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>41.33</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1347</t>
-        </is>
-      </c>
-      <c r="BA16" t="inlineStr"/>
-      <c r="BB16" t="inlineStr"/>
-      <c r="BC16" t="inlineStr"/>
-      <c r="BD16" t="inlineStr"/>
-      <c r="BE16" t="inlineStr"/>
-      <c r="BF16" t="inlineStr"/>
+          <t>0.1287</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>6.85</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>36.39</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>87.72</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>0.368</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>0.1417</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>28.41</t>
+        </is>
+      </c>
       <c r="BG16" t="inlineStr"/>
       <c r="BH16" t="inlineStr"/>
       <c r="BI16" t="inlineStr">
@@ -4690,7 +4690,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="Q17" t="n">
         <v>33.4</v>
@@ -4714,7 +4714,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>70.22</t>
+          <t>70.15</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
@@ -4899,12 +4899,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>810938</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ben Williamson</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -4929,14 +4929,14 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>30</v>
+        <v>30.3</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>11.6</v>
+        <v>0.2</v>
       </c>
       <c r="Q18" t="n">
         <v>41.2</v>
@@ -4963,13 +4963,13 @@
         <v>27.6</v>
       </c>
       <c r="S18" t="n">
-        <v>47.9</v>
+        <v>71.7</v>
       </c>
       <c r="T18" t="n">
         <v>60</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>15.3</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -4978,12 +4978,12 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -5025,12 +5025,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/19, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -5055,67 +5055,67 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>35.39</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>98.4446</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3241</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0789</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2809</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>69.49</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>27.55</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.0731</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr"/>
@@ -5218,7 +5218,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>68.35</t>
+          <t>68.28</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
@@ -5735,14 +5735,14 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>54.4</v>
+        <v>54.7</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         <v>27.6</v>
       </c>
       <c r="S2" t="n">
-        <v>90.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T2" t="n">
         <v>60</v>
@@ -5784,12 +5784,12 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>72.67</t>
+          <t>72.74</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
@@ -6552,7 +6552,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Yandy Diaz</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -6767,14 +6767,14 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>46.6</v>
+        <v>46.4</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>43.3</v>
+        <v>41</v>
       </c>
       <c r="Q6" t="n">
         <v>41.2</v>
@@ -6801,13 +6801,13 @@
         <v>27.6</v>
       </c>
       <c r="S6" t="n">
-        <v>92.09999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="T6" t="n">
         <v>60</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>20.9</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -6816,12 +6816,12 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -6863,12 +6863,12 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -6878,7 +6878,7 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -6893,67 +6893,67 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>102.6273</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1288</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr"/>
@@ -6977,12 +6977,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>668723</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Ryan Vilade</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -7032,7 +7032,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>41</v>
+        <v>43.3</v>
       </c>
       <c r="Q7" t="n">
         <v>41.2</v>
@@ -7041,13 +7041,13 @@
         <v>27.6</v>
       </c>
       <c r="S7" t="n">
-        <v>88.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T7" t="n">
         <v>60</v>
       </c>
       <c r="U7" t="n">
-        <v>20.9</v>
+        <v>0</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -7056,12 +7056,12 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -7103,12 +7103,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -7133,67 +7133,67 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>50.43</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>91.42</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>102.6273</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.3949</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1562</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3174</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>75.84</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>37.37</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1617</t>
+          <t>0.1288</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr"/>
@@ -7308,7 +7308,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -7584,7 +7584,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -7836,7 +7836,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
       <c r="Q10" t="n">
         <v>31.6</v>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -7972,7 +7972,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>72.34</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -8045,24 +8045,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -8075,26 +8075,14 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Freddy Peralta</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>642547</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>36.9</v>
+        <v>37.9</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8108,26 +8096,26 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>20.9</v>
+        <v>10.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>33.4</v>
+        <v>41.2</v>
       </c>
       <c r="R11" t="n">
         <v>27.6</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U11" t="n">
-        <v>12</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -8136,24 +8124,24 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -8166,7 +8154,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -8183,27 +8171,27 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -8213,99 +8201,75 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>98.2866</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.163</t>
-        </is>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>6.85</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>36.39</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>87.72</t>
-        </is>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>0.368</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>0.1417</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>28.41</t>
-        </is>
-      </c>
+          <t>0.151</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr"/>
       <c r="BG11" t="inlineStr"/>
       <c r="BH11" t="inlineStr"/>
       <c r="BI11" t="inlineStr">
@@ -8321,24 +8285,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -8354,11 +8318,23 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Freddy Peralta</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>642547</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L12" t="n">
-        <v>36.5</v>
+        <v>36.9</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8372,14 +8348,14 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>10.6</v>
+        <v>21</v>
       </c>
       <c r="Q12" t="n">
-        <v>41.2</v>
+        <v>33.4</v>
       </c>
       <c r="R12" t="n">
         <v>27.6</v>
@@ -8388,10 +8364,10 @@
         <v>71.7</v>
       </c>
       <c r="T12" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>70.59999999999999</v>
+        <v>12</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -8400,24 +8376,24 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -8430,7 +8406,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -8447,27 +8423,27 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -8477,75 +8453,99 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>98.2866</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.123</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>72.68</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.151</t>
-        </is>
-      </c>
-      <c r="BA12" t="inlineStr"/>
-      <c r="BB12" t="inlineStr"/>
-      <c r="BC12" t="inlineStr"/>
-      <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="inlineStr"/>
-      <c r="BF12" t="inlineStr"/>
+          <t>0.163</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>6.85</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>36.39</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>87.72</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>0.368</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>0.1417</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>28.41</t>
+        </is>
+      </c>
       <c r="BG12" t="inlineStr"/>
       <c r="BH12" t="inlineStr"/>
       <c r="BI12" t="inlineStr">
@@ -8652,7 +8652,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -8837,24 +8837,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>677587</t>
+          <t>622761</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Jorge Mateo</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -8867,26 +8867,14 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Freddy Peralta</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>642547</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>32.3</v>
+        <v>33.9</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -8900,26 +8888,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>13.7</v>
+        <v>23.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>31.6</v>
+        <v>41.2</v>
       </c>
       <c r="R14" t="n">
         <v>27.6</v>
       </c>
       <c r="S14" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T14" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="U14" t="n">
-        <v>72.7</v>
+        <v>0.8</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -8928,24 +8916,24 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -8958,7 +8946,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -8975,27 +8963,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 2/16, 0 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -9005,99 +8993,75 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>6.76</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>35.51</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>97.253</t>
+          <t>98.4476</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3524</t>
+          <t>0.3271</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1067</t>
+          <t>0.1223</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.2943</t>
+          <t>0.2522</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>69.79</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>31.46</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>29.09</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.1287</t>
-        </is>
-      </c>
-      <c r="BA14" t="inlineStr">
-        <is>
-          <t>6.85</t>
-        </is>
-      </c>
-      <c r="BB14" t="inlineStr">
-        <is>
-          <t>36.39</t>
-        </is>
-      </c>
-      <c r="BC14" t="inlineStr">
-        <is>
-          <t>87.72</t>
-        </is>
-      </c>
-      <c r="BD14" t="inlineStr">
-        <is>
-          <t>0.368</t>
-        </is>
-      </c>
-      <c r="BE14" t="inlineStr">
-        <is>
-          <t>0.1417</t>
-        </is>
-      </c>
-      <c r="BF14" t="inlineStr">
-        <is>
-          <t>28.41</t>
-        </is>
-      </c>
+          <t>0.1044</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr"/>
+      <c r="BB14" t="inlineStr"/>
+      <c r="BC14" t="inlineStr"/>
+      <c r="BD14" t="inlineStr"/>
+      <c r="BE14" t="inlineStr"/>
+      <c r="BF14" t="inlineStr"/>
       <c r="BG14" t="inlineStr"/>
       <c r="BH14" t="inlineStr"/>
       <c r="BI14" t="inlineStr">
@@ -9113,12 +9077,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>663743</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Nick Fortes</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -9143,14 +9107,14 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>31.8</v>
+        <v>32.9</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9168,7 +9132,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0.2</v>
+        <v>12.8</v>
       </c>
       <c r="Q15" t="n">
         <v>41.2</v>
@@ -9177,13 +9141,13 @@
         <v>27.6</v>
       </c>
       <c r="S15" t="n">
-        <v>81.90000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="T15" t="n">
         <v>60</v>
       </c>
       <c r="U15" t="n">
-        <v>15.3</v>
+        <v>18.3</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -9192,12 +9156,12 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -9239,22 +9203,22 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 2/17, 1 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -9269,67 +9233,67 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>36.15</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>86.03</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>99.0812</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3248</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.093</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.2721</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>72.49</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>50.84</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>18.36</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.1186</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr"/>
@@ -9353,24 +9317,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>689414</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -9383,14 +9347,26 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Freddy Peralta</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>642547</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L16" t="n">
-        <v>31.4</v>
+        <v>32.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -9404,26 +9380,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>7.8</v>
+        <v>13.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>41.2</v>
+        <v>31.6</v>
       </c>
       <c r="R16" t="n">
         <v>27.6</v>
       </c>
       <c r="S16" t="n">
-        <v>59.8</v>
+        <v>40.2</v>
       </c>
       <c r="T16" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="U16" t="n">
-        <v>19.5</v>
+        <v>72.7</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -9432,24 +9408,24 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -9462,7 +9438,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -9479,27 +9455,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -9509,75 +9485,99 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>96.0847</t>
+          <t>97.253</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3556</t>
+          <t>0.3524</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.0997</t>
+          <t>0.1067</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3178</t>
+          <t>0.2943</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>68.03</t>
+          <t>69.79</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>41.33</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1347</t>
-        </is>
-      </c>
-      <c r="BA16" t="inlineStr"/>
-      <c r="BB16" t="inlineStr"/>
-      <c r="BC16" t="inlineStr"/>
-      <c r="BD16" t="inlineStr"/>
-      <c r="BE16" t="inlineStr"/>
-      <c r="BF16" t="inlineStr"/>
+          <t>0.1287</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>6.85</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>36.39</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>87.72</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>0.368</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>0.1417</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>28.41</t>
+        </is>
+      </c>
       <c r="BG16" t="inlineStr"/>
       <c r="BH16" t="inlineStr"/>
       <c r="BI16" t="inlineStr">
@@ -9660,7 +9660,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="Q17" t="n">
         <v>33.4</v>
@@ -9684,7 +9684,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>70.22</t>
+          <t>70.15</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
@@ -9869,12 +9869,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>810938</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ben Williamson</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -9899,14 +9899,14 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>30</v>
+        <v>30.3</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -9924,7 +9924,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>11.6</v>
+        <v>0.2</v>
       </c>
       <c r="Q18" t="n">
         <v>41.2</v>
@@ -9933,13 +9933,13 @@
         <v>27.6</v>
       </c>
       <c r="S18" t="n">
-        <v>47.9</v>
+        <v>71.7</v>
       </c>
       <c r="T18" t="n">
         <v>60</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>15.3</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -9948,12 +9948,12 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -10010,7 +10010,7 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/19, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -10025,67 +10025,67 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>35.39</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>98.4446</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3241</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0789</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2809</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>69.49</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>27.55</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.0731</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr"/>
@@ -10188,7 +10188,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -10300,7 +10300,7 @@
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>68.35</t>
+          <t>68.28</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-10-19.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-19.xlsx
@@ -760,12 +760,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>51.5</v>
+        <v>53.9</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -808,10 +808,10 @@
         <v>32</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>50</v>
@@ -821,39 +821,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -996,8 +992,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -1036,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1060,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>50</v>
+        <v>52.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1074,7 +1078,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1084,10 +1088,10 @@
         <v>32</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S3" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -1097,39 +1101,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1272,8 +1272,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -1312,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1336,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>48.7</v>
+        <v>51.2</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1350,7 +1358,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1360,10 +1368,10 @@
         <v>33.4</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S4" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
@@ -1373,14 +1381,14 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X4" t="inlineStr">
         <is>
           <t>4</t>
@@ -1398,12 +1406,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1548,8 +1556,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -1588,7 +1604,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1612,7 +1628,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>46.6</v>
+        <v>49.2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1626,7 +1642,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1636,10 +1652,10 @@
         <v>33.4</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S5" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
@@ -1649,14 +1665,14 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X5" t="inlineStr">
         <is>
           <t>3</t>
@@ -1674,12 +1690,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1824,8 +1840,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -1839,24 +1863,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Victor Mesa Jr.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -1864,22 +1888,22 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1888,7 +1912,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>43.3</v>
+        <v>48.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1902,62 +1926,58 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>36.3</v>
+        <v>43.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>33.4</v>
+        <v>32</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S6" t="n">
-        <v>81.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>10.1</v>
+        <v>54.9</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1977,27 +1997,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -2007,101 +2027,109 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>100.2811</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3305</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>32.53</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>40.38</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1803</t>
+          <t>0.2134</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>28.41</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+          <t>29.92</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -2115,24 +2143,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -2140,22 +2168,22 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -2164,7 +2192,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>43.3</v>
+        <v>45.9</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2178,40 +2206,40 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>41</v>
+        <v>36.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>32</v>
+        <v>33.4</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S7" t="n">
-        <v>88.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>20.9</v>
+        <v>10.1</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -2226,12 +2254,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -2253,12 +2281,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -2268,12 +2296,12 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -2283,101 +2311,109 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1617</t>
+          <t>0.1803</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>29.92</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+          <t>28.41</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -2391,12 +2427,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2416,12 +2452,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2440,7 +2476,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>43.3</v>
+        <v>45.9</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2454,62 +2490,58 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>43.3</v>
+        <v>41</v>
       </c>
       <c r="Q8" t="n">
         <v>32</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S8" t="n">
-        <v>90.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T8" t="n">
         <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>20.9</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2529,12 +2561,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -2544,7 +2576,7 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2559,67 +2591,67 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>102.6273</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1288</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2652,8 +2684,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -2672,7 +2712,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2692,7 +2732,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2716,7 +2756,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>41.5</v>
+        <v>44.1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2730,7 +2770,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -2740,10 +2780,10 @@
         <v>31.6</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S9" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T9" t="n">
         <v>75</v>
@@ -2753,14 +2793,14 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X9" t="inlineStr">
         <is>
           <t>2</t>
@@ -2778,12 +2818,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -2928,8 +2968,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -2968,7 +3016,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -2992,7 +3040,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>40</v>
+        <v>42.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3006,7 +3054,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -3016,10 +3064,10 @@
         <v>31.6</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S10" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
         <v>75</v>
@@ -3029,14 +3077,14 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X10" t="inlineStr">
         <is>
           <t>7</t>
@@ -3054,12 +3102,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -3204,8 +3252,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -3244,7 +3300,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3268,7 +3324,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>36.9</v>
+        <v>39.5</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3282,7 +3338,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -3292,10 +3348,10 @@
         <v>33.4</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T11" t="n">
         <v>80</v>
@@ -3305,14 +3361,14 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X11" t="inlineStr">
         <is>
           <t>6</t>
@@ -3330,12 +3386,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -3480,8 +3536,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -3495,24 +3559,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>680757</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -3520,22 +3584,22 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -3544,7 +3608,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>34.9</v>
+        <v>38</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3558,62 +3622,58 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.9</v>
+        <v>7.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>33.4</v>
+        <v>32</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S12" t="n">
-        <v>88.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>43.1</v>
+        <v>19.5</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3633,12 +3693,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -3648,12 +3708,12 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -3663,101 +3723,109 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>84.59</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>92.8324</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.3499</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.0741</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>62.73</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.0775</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>28.41</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+          <t>29.92</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -3771,24 +3839,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -3796,22 +3864,22 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -3820,7 +3888,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>34.8</v>
+        <v>37.5</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3834,40 +3902,40 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>10.6</v>
+        <v>2.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>32</v>
+        <v>33.4</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S13" t="n">
-        <v>81.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>70.59999999999999</v>
+        <v>43.1</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -3882,12 +3950,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -3909,27 +3977,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -3939,101 +4007,109 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>84.59</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>92.8324</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>62.73</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.0775</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>29.92</t>
-        </is>
-      </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+          <t>28.41</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -4072,7 +4148,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4096,7 +4172,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>32.3</v>
+        <v>34.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4110,7 +4186,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -4120,10 +4196,10 @@
         <v>31.6</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S14" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T14" t="n">
         <v>75</v>
@@ -4133,14 +4209,14 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X14" t="inlineStr">
         <is>
           <t>9</t>
@@ -4158,12 +4234,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -4308,8 +4384,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -4323,12 +4407,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>622761</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jorge Mateo</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4348,7 +4432,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4372,7 +4456,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>30.7</v>
+        <v>34.4</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4386,62 +4470,58 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>23.3</v>
+        <v>15.4</v>
       </c>
       <c r="Q15" t="n">
         <v>32</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8</v>
+        <v>19.5</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4461,12 +4541,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -4476,12 +4556,12 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4491,67 +4571,67 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>98.4476</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3271</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1223</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2522</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1044</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -4584,8 +4664,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -4599,24 +4687,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>690984</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -4624,22 +4712,22 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -4648,7 +4736,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>30.3</v>
+        <v>34.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4662,62 +4750,58 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>7</v>
+        <v>10.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>33.4</v>
+        <v>32</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>38.3</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4737,27 +4821,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Contact streak: 3/8 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -4767,101 +4851,109 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>93.4449</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3143</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2902</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>70.15</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.0707</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>28.41</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+          <t>29.92</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -4900,12 +4992,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -4924,7 +5016,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>29.9</v>
+        <v>33.9</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4938,7 +5030,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -4948,10 +5040,10 @@
         <v>32</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S17" t="n">
-        <v>71.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T17" t="n">
         <v>80</v>
@@ -4961,39 +5053,35 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5136,8 +5224,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -5151,24 +5247,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>663743</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nick Fortes</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -5176,22 +5272,22 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -5200,7 +5296,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>29.8</v>
+        <v>32.9</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5214,40 +5310,40 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>12.8</v>
+        <v>7</v>
       </c>
       <c r="Q18" t="n">
-        <v>32</v>
+        <v>33.4</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>18.3</v>
+        <v>38.3</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -5262,12 +5358,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -5289,27 +5385,27 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/17, 1 HR</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -5319,101 +5415,109 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>86.03</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>99.0812</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3248</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2721</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>72.49</t>
+          <t>70.15</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>29.92</t>
-        </is>
-      </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+          <t>28.41</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -5452,7 +5556,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5476,7 +5580,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>27.3</v>
+        <v>29.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5490,7 +5594,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -5500,10 +5604,10 @@
         <v>31.5</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -5513,39 +5617,35 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5688,8 +5788,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -6054,12 +6162,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -6078,7 +6186,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>51.5</v>
+        <v>53.9</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6092,7 +6200,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -6102,10 +6210,10 @@
         <v>32</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>50</v>
@@ -6115,39 +6223,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6290,8 +6394,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -6330,7 +6442,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -6354,7 +6466,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>50</v>
+        <v>52.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6368,7 +6480,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -6378,10 +6490,10 @@
         <v>32</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S3" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -6391,39 +6503,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6566,8 +6674,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -6606,7 +6722,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -6630,7 +6746,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>48.7</v>
+        <v>51.2</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6644,7 +6760,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -6654,10 +6770,10 @@
         <v>33.4</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S4" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
@@ -6667,14 +6783,14 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X4" t="inlineStr">
         <is>
           <t>4</t>
@@ -6692,12 +6808,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -6842,8 +6958,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -6882,7 +7006,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -6906,7 +7030,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>46.6</v>
+        <v>49.2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -6920,7 +7044,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -6930,10 +7054,10 @@
         <v>33.4</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S5" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
@@ -6943,14 +7067,14 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X5" t="inlineStr">
         <is>
           <t>3</t>
@@ -6968,12 +7092,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -7118,8 +7242,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -7133,24 +7265,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Victor Mesa Jr.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -7158,22 +7290,22 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -7182,7 +7314,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>43.3</v>
+        <v>48.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7196,62 +7328,58 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>36.3</v>
+        <v>43.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>33.4</v>
+        <v>32</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S6" t="n">
-        <v>81.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>10.1</v>
+        <v>54.9</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7271,27 +7399,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -7301,101 +7429,109 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>100.2811</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3305</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>32.53</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>40.38</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1803</t>
+          <t>0.2134</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>28.41</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+          <t>29.92</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -7409,24 +7545,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -7434,22 +7570,22 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -7458,7 +7594,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>43.3</v>
+        <v>45.9</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7472,40 +7608,40 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>41</v>
+        <v>36.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>32</v>
+        <v>33.4</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S7" t="n">
-        <v>88.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>20.9</v>
+        <v>10.1</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -7520,12 +7656,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -7547,12 +7683,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -7562,12 +7698,12 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -7577,101 +7713,109 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1617</t>
+          <t>0.1803</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>29.92</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+          <t>28.41</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -7685,12 +7829,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -7710,12 +7854,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -7734,7 +7878,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>43.3</v>
+        <v>45.9</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7748,62 +7892,58 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>43.3</v>
+        <v>41</v>
       </c>
       <c r="Q8" t="n">
         <v>32</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S8" t="n">
-        <v>90.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T8" t="n">
         <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>20.9</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7823,12 +7963,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -7838,7 +7978,7 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -7853,67 +7993,67 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>102.6273</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1288</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -7946,8 +8086,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -7966,7 +8114,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -7986,7 +8134,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -8010,7 +8158,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>41.5</v>
+        <v>44.1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8024,7 +8172,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -8034,10 +8182,10 @@
         <v>31.6</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S9" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T9" t="n">
         <v>75</v>
@@ -8047,14 +8195,14 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X9" t="inlineStr">
         <is>
           <t>2</t>
@@ -8072,12 +8220,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -8222,8 +8370,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -8262,7 +8418,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -8286,7 +8442,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>40</v>
+        <v>42.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8300,7 +8456,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -8310,10 +8466,10 @@
         <v>31.6</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S10" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
         <v>75</v>
@@ -8323,14 +8479,14 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X10" t="inlineStr">
         <is>
           <t>7</t>
@@ -8348,12 +8504,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -8498,8 +8654,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -8538,7 +8702,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -8562,7 +8726,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>36.9</v>
+        <v>39.5</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8576,7 +8740,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -8586,10 +8750,10 @@
         <v>33.4</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T11" t="n">
         <v>80</v>
@@ -8599,14 +8763,14 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X11" t="inlineStr">
         <is>
           <t>6</t>
@@ -8624,12 +8788,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -8774,8 +8938,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -8789,24 +8961,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>680757</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -8814,22 +8986,22 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -8838,7 +9010,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>34.9</v>
+        <v>38</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8852,62 +9024,58 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.9</v>
+        <v>7.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>33.4</v>
+        <v>32</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S12" t="n">
-        <v>88.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>43.1</v>
+        <v>19.5</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8927,12 +9095,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -8942,12 +9110,12 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -8957,101 +9125,109 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>84.59</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>92.8324</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.3499</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.0741</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>62.73</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.0775</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>28.41</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+          <t>29.92</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -9065,24 +9241,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -9090,22 +9266,22 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -9114,7 +9290,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>34.8</v>
+        <v>37.5</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9128,40 +9304,40 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>10.6</v>
+        <v>2.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>32</v>
+        <v>33.4</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S13" t="n">
-        <v>81.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>70.59999999999999</v>
+        <v>43.1</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -9176,12 +9352,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -9203,27 +9379,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -9233,101 +9409,109 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>84.59</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>92.8324</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>62.73</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.0775</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>29.92</t>
-        </is>
-      </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+          <t>28.41</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -9366,7 +9550,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -9390,7 +9574,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>32.3</v>
+        <v>34.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9404,7 +9588,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -9414,10 +9598,10 @@
         <v>31.6</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S14" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T14" t="n">
         <v>75</v>
@@ -9427,14 +9611,14 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X14" t="inlineStr">
         <is>
           <t>9</t>
@@ -9452,12 +9636,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -9602,8 +9786,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -9617,12 +9809,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>622761</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jorge Mateo</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -9642,7 +9834,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -9666,7 +9858,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>30.7</v>
+        <v>34.4</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9680,62 +9872,58 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>23.3</v>
+        <v>15.4</v>
       </c>
       <c r="Q15" t="n">
         <v>32</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8</v>
+        <v>19.5</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9755,12 +9943,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -9770,12 +9958,12 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -9785,67 +9973,67 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>98.4476</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3271</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1223</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2522</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1044</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -9878,8 +10066,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -9893,24 +10089,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>690984</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -9918,22 +10114,22 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -9942,7 +10138,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>30.3</v>
+        <v>34.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -9956,62 +10152,58 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>7</v>
+        <v>10.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>33.4</v>
+        <v>32</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>38.3</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10031,27 +10223,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Contact streak: 3/8 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -10061,101 +10253,109 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>93.4449</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3143</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2902</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>70.15</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.0707</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>28.41</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+          <t>29.92</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -10194,12 +10394,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -10218,7 +10418,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>29.9</v>
+        <v>33.9</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10232,7 +10432,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -10242,10 +10442,10 @@
         <v>32</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S17" t="n">
-        <v>71.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T17" t="n">
         <v>80</v>
@@ -10255,39 +10455,35 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10430,8 +10626,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -10445,24 +10649,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>663743</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nick Fortes</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -10470,22 +10674,22 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -10494,7 +10698,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>29.8</v>
+        <v>32.9</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10508,40 +10712,40 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>12.8</v>
+        <v>7</v>
       </c>
       <c r="Q18" t="n">
-        <v>32</v>
+        <v>33.4</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>18.3</v>
+        <v>38.3</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -10556,12 +10760,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -10583,27 +10787,27 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/17, 1 HR</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -10613,101 +10817,109 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>86.03</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>99.0812</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3248</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2721</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>72.49</t>
+          <t>70.15</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>29.92</t>
-        </is>
-      </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+          <t>28.41</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -10746,7 +10958,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -10770,7 +10982,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>27.3</v>
+        <v>29.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10784,7 +10996,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -10794,10 +11006,10 @@
         <v>31.5</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -10807,39 +11019,35 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10982,8 +11190,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Tropicana Field</t>

--- a/outputs/daily/hr_rankings_2026-10-19.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-19.xlsx
@@ -1386,34 +1386,30 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1670,34 +1666,30 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -2234,34 +2226,30 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2798,34 +2786,30 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3082,34 +3066,30 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3366,34 +3346,30 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -3930,34 +3906,30 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4214,34 +4186,30 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5338,34 +5306,30 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6788,34 +6752,30 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7072,34 +7032,30 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -7636,34 +7592,30 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8200,34 +8152,30 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8484,34 +8432,30 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8768,34 +8712,30 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -9332,34 +9272,30 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9616,34 +9552,30 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10740,34 +10672,30 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
